--- a/VT_VASUDHA_PRI_V01.xlsx
+++ b/VT_VASUDHA_PRI_V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda_models\Vasudha Exercise\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaura\Documents\GitHub\Vasudha Exercise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1476D4AB-29D6-49AB-AC1F-6A8497FB0B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4AB2FD6-D003-43ED-B19D-95F46EF774F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="901" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="901" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand_Projection" sheetId="142" r:id="rId1"/>
@@ -52,7 +52,7 @@
     <definedName name="base.year">'[1]Target Year Input'!$E$3</definedName>
     <definedName name="btu_per_watthr">#REF!</definedName>
     <definedName name="Clean">#REF!</definedName>
-    <definedName name="coal.past">'[1]XV.b.o'!$B$12:$G$23</definedName>
+    <definedName name="coal.past">[1]XV.b.o!$B$12:$G$23</definedName>
     <definedName name="Constants.Density.Diesel">#REF!</definedName>
     <definedName name="Constants.Density.Ethanol">#REF!</definedName>
     <definedName name="Constants.Density.JetFuel">#REF!</definedName>
@@ -178,7 +178,7 @@
     <definedName name="m_space">#REF!</definedName>
     <definedName name="MAXREC">#REF!</definedName>
     <definedName name="MGBP">[1]Conversions!$E$108</definedName>
-    <definedName name="Minesize.xv.b">'[1]XV.b.o'!$D$118</definedName>
+    <definedName name="Minesize.xv.b">[1]XV.b.o!$D$118</definedName>
     <definedName name="Non_fuel_OM">#REF!</definedName>
     <definedName name="NONLEAP">#REF!</definedName>
     <definedName name="nuclear.past">#REF!</definedName>
@@ -336,17 +336,6 @@
     <definedName name="xvi.scenario.fuelsplit">[1]Control!$E$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -2650,7 +2639,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="145">
   <si>
     <t>CommName</t>
   </si>
@@ -3082,6 +3071,9 @@
   </si>
   <si>
     <t>by</t>
+  </si>
+  <si>
+    <t>DIIS</t>
   </si>
 </sst>
 </file>
@@ -6440,12 +6432,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8AD745C-D4E7-4422-90FA-496888C7C801}">
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="53" t="s">
         <v>136</v>
       </c>
@@ -6459,7 +6451,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="48">
         <v>2000</v>
       </c>
@@ -6475,7 +6467,7 @@
         <v>7.578527216468367E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="48">
         <v>2001</v>
       </c>
@@ -6484,7 +6476,7 @@
       </c>
       <c r="C4" s="48"/>
     </row>
-    <row r="5" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="48">
         <v>2002</v>
       </c>
@@ -6493,7 +6485,7 @@
       </c>
       <c r="C5" s="48"/>
     </row>
-    <row r="6" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="48">
         <v>2003</v>
       </c>
@@ -6502,7 +6494,7 @@
       </c>
       <c r="C6" s="48"/>
     </row>
-    <row r="7" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="48">
         <v>2004</v>
       </c>
@@ -6511,7 +6503,7 @@
       </c>
       <c r="C7" s="48"/>
     </row>
-    <row r="8" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="48">
         <v>2005</v>
       </c>
@@ -6520,7 +6512,7 @@
       </c>
       <c r="C8" s="48"/>
     </row>
-    <row r="9" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="48">
         <v>2006</v>
       </c>
@@ -6529,7 +6521,7 @@
       </c>
       <c r="C9" s="48"/>
     </row>
-    <row r="10" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="48">
         <v>2007</v>
       </c>
@@ -6538,7 +6530,7 @@
       </c>
       <c r="C10" s="48"/>
     </row>
-    <row r="11" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="48">
         <v>2008</v>
       </c>
@@ -6547,7 +6539,7 @@
       </c>
       <c r="C11" s="48"/>
     </row>
-    <row r="12" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="48">
         <v>2009</v>
       </c>
@@ -6556,7 +6548,7 @@
       </c>
       <c r="C12" s="48"/>
     </row>
-    <row r="13" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="48">
         <v>2010</v>
       </c>
@@ -6565,7 +6557,7 @@
       </c>
       <c r="C13" s="48"/>
     </row>
-    <row r="14" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="48">
         <v>2011</v>
       </c>
@@ -6574,7 +6566,7 @@
       </c>
       <c r="C14" s="48"/>
     </row>
-    <row r="15" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="48">
         <v>2012</v>
       </c>
@@ -6583,7 +6575,7 @@
       </c>
       <c r="C15" s="48"/>
     </row>
-    <row r="16" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="48">
         <v>2013</v>
       </c>
@@ -6592,7 +6584,7 @@
       </c>
       <c r="C16" s="48"/>
     </row>
-    <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="48">
         <v>2014</v>
       </c>
@@ -6601,7 +6593,7 @@
       </c>
       <c r="C17" s="48"/>
     </row>
-    <row r="18" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="48">
         <v>2015</v>
       </c>
@@ -6610,7 +6602,7 @@
       </c>
       <c r="C18" s="48"/>
     </row>
-    <row r="19" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="48">
         <v>2016</v>
       </c>
@@ -6619,7 +6611,7 @@
       </c>
       <c r="C19" s="48"/>
     </row>
-    <row r="20" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="48">
         <v>2017</v>
       </c>
@@ -6628,7 +6620,7 @@
       </c>
       <c r="C20" s="48"/>
     </row>
-    <row r="21" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="48">
         <v>2018</v>
       </c>
@@ -6637,7 +6629,7 @@
       </c>
       <c r="C21" s="48"/>
     </row>
-    <row r="22" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="48">
         <v>2019</v>
       </c>
@@ -6646,7 +6638,7 @@
       </c>
       <c r="C22" s="48"/>
     </row>
-    <row r="23" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="48">
         <v>2020</v>
       </c>
@@ -6655,7 +6647,7 @@
       </c>
       <c r="C23" s="48"/>
     </row>
-    <row r="24" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="48">
         <v>2021</v>
       </c>
@@ -6664,7 +6656,7 @@
       </c>
       <c r="C24" s="48"/>
     </row>
-    <row r="25" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="48">
         <v>2022</v>
       </c>
@@ -6673,7 +6665,7 @@
       </c>
       <c r="C25" s="48"/>
     </row>
-    <row r="26" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="48">
         <v>2023</v>
       </c>
@@ -6685,7 +6677,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="48">
         <v>2024</v>
       </c>
@@ -6695,7 +6687,7 @@
       </c>
       <c r="C27" s="48"/>
     </row>
-    <row r="28" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="48">
         <v>2025</v>
       </c>
@@ -6705,7 +6697,7 @@
       </c>
       <c r="C28" s="48"/>
     </row>
-    <row r="29" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="48">
         <v>2026</v>
       </c>
@@ -6715,7 +6707,7 @@
       </c>
       <c r="C29" s="48"/>
     </row>
-    <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="48">
         <v>2027</v>
       </c>
@@ -6725,7 +6717,7 @@
       </c>
       <c r="C30" s="48"/>
     </row>
-    <row r="31" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="48">
         <v>2028</v>
       </c>
@@ -6735,7 +6727,7 @@
       </c>
       <c r="C31" s="48"/>
     </row>
-    <row r="32" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="48">
         <v>2029</v>
       </c>
@@ -6745,7 +6737,7 @@
       </c>
       <c r="C32" s="48"/>
     </row>
-    <row r="33" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="48">
         <v>2030</v>
       </c>
@@ -6755,7 +6747,7 @@
       </c>
       <c r="C33" s="48"/>
     </row>
-    <row r="34" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="48">
         <v>2031</v>
       </c>
@@ -6765,7 +6757,7 @@
       </c>
       <c r="C34" s="48"/>
     </row>
-    <row r="35" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="48">
         <v>2032</v>
       </c>
@@ -6775,7 +6767,7 @@
       </c>
       <c r="C35" s="48"/>
     </row>
-    <row r="36" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="48">
         <v>2033</v>
       </c>
@@ -6785,7 +6777,7 @@
       </c>
       <c r="C36" s="48"/>
     </row>
-    <row r="37" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="48">
         <v>2034</v>
       </c>
@@ -6795,7 +6787,7 @@
       </c>
       <c r="C37" s="48"/>
     </row>
-    <row r="38" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="48">
         <v>2035</v>
       </c>
@@ -6805,7 +6797,7 @@
       </c>
       <c r="C38" s="48"/>
     </row>
-    <row r="39" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="48">
         <v>2036</v>
       </c>
@@ -6815,7 +6807,7 @@
       </c>
       <c r="C39" s="48"/>
     </row>
-    <row r="40" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="48">
         <v>2037</v>
       </c>
@@ -6825,7 +6817,7 @@
       </c>
       <c r="C40" s="48"/>
     </row>
-    <row r="41" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="48">
         <v>2038</v>
       </c>
@@ -6835,7 +6827,7 @@
       </c>
       <c r="C41" s="48"/>
     </row>
-    <row r="42" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="48">
         <v>2039</v>
       </c>
@@ -6845,7 +6837,7 @@
       </c>
       <c r="C42" s="48"/>
     </row>
-    <row r="43" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="48">
         <v>2040</v>
       </c>
@@ -6866,10 +6858,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{286771AF-ECD8-482D-A125-D9EAB038D799}">
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -7120,13 +7112,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9C7149-FB43-4FB6-89C2-AE696F79846A}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>121</v>
       </c>
@@ -7134,7 +7126,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>Fuel_Code!A2&amp;Fuel_Code!A14</f>
         <v>MINCOACC</v>
@@ -7144,7 +7136,7 @@
         <v>Domestic Production of Coking Coal</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>Fuel_Code!A2&amp;Fuel_Code!A15</f>
         <v>MINCOANCC</v>
@@ -7154,7 +7146,7 @@
         <v>Domestic Production of Non Coking Coal</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>Fuel_Code!A3&amp;Fuel_Code!A14</f>
         <v>IMPCOACC</v>
@@ -7164,7 +7156,7 @@
         <v>Import of Coking Coal</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>Fuel_Code!A3&amp;Fuel_Code!A15</f>
         <v>IMPCOANCC</v>
@@ -7174,7 +7166,7 @@
         <v>Import by Non Coking Coal</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>Fuel_Code!A4&amp;Fuel_Code!A15</f>
         <v>EXPCOANCC</v>
@@ -7184,7 +7176,7 @@
         <v>Export of Non Coking Coal</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>Fuel_Code!A2&amp;Fuel_Code!A21</f>
         <v>MINGASNAT</v>
@@ -7194,7 +7186,7 @@
         <v xml:space="preserve">Domestic Production of Natural Gas </v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>Fuel_Code!A3&amp;Fuel_Code!A21</f>
         <v>IMPGASNAT</v>
@@ -7204,7 +7196,7 @@
         <v xml:space="preserve">Import of Natural Gas </v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>Fuel_Code!$A$2&amp;Fuel_Code!A22</f>
         <v>MINH2GRY</v>
@@ -7214,7 +7206,7 @@
         <v>Domestic Production of Hydrogen - Grey</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>Fuel_Code!$A$2&amp;Fuel_Code!A23</f>
         <v>MINH2GRN</v>
@@ -7224,7 +7216,7 @@
         <v>Domestic Production of Hydorgen Green</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>Fuel_Code!A2&amp;Fuel_Code!A20</f>
         <v>MINELT</v>
@@ -7234,7 +7226,7 @@
         <v>Electricity</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A12" s="46" t="str">
         <f>Fuel_Code!A$28&amp;Fuel_Code!A29</f>
         <v>IISBF-BOF</v>
@@ -7244,7 +7236,7 @@
         <v>Steel Production by Blast Furnace Basic Oxygen Furnace</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="13.25" x14ac:dyDescent="0.25">
       <c r="A13" s="46" t="str">
         <f>Fuel_Code!A$28&amp;Fuel_Code!A30</f>
         <v>IISDRI</v>
@@ -7262,31 +7254,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:V28"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" customWidth="1"/>
-    <col min="12" max="12" width="4.44140625" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="48.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.109375" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" customWidth="1"/>
-    <col min="19" max="19" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.36328125" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" customWidth="1"/>
+    <col min="12" max="12" width="4.453125" customWidth="1"/>
+    <col min="13" max="13" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.08984375" customWidth="1"/>
+    <col min="18" max="18" width="11.54296875" customWidth="1"/>
+    <col min="19" max="19" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B1" s="13" t="s">
         <v>52</v>
       </c>
@@ -7305,7 +7297,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B2" s="8"/>
       <c r="C2" s="8" t="str">
         <f>Fuel_Code!A13</f>
@@ -7333,7 +7325,7 @@
       <c r="T2" s="38"/>
       <c r="U2" s="38"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" ht="13" x14ac:dyDescent="0.3">
       <c r="M3" s="39" t="s">
         <v>7</v>
       </c>
@@ -7362,7 +7354,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
       <c r="M4" s="41" t="s">
         <v>38</v>
@@ -7392,7 +7384,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C5" s="8"/>
       <c r="M5" s="38" t="s">
         <v>51</v>
@@ -7505,14 +7497,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" ht="13" x14ac:dyDescent="0.3">
       <c r="E10" s="5" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="5"/>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" ht="13" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
         <v>1</v>
       </c>
@@ -7552,7 +7544,7 @@
       <c r="T11" s="42"/>
       <c r="U11" s="42"/>
     </row>
-    <row r="12" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="21.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B12" s="10" t="s">
         <v>40</v>
       </c>
@@ -7600,7 +7592,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="10" t="s">
         <v>64</v>
       </c>
@@ -7649,7 +7641,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:21" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="38" t="str">
         <f>O15</f>
         <v>MINCOACC</v>
@@ -8081,31 +8073,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{589F79F9-1573-4116-B551-AAEB4823F41D}">
   <dimension ref="A1:U27"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6640625" customWidth="1"/>
-    <col min="12" max="12" width="4.44140625" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="48.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.109375" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" customWidth="1"/>
-    <col min="19" max="19" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.36328125" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" customWidth="1"/>
+    <col min="12" max="12" width="4.453125" customWidth="1"/>
+    <col min="13" max="13" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.08984375" customWidth="1"/>
+    <col min="18" max="18" width="11.54296875" customWidth="1"/>
+    <col min="19" max="19" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B1" s="13" t="s">
         <v>52</v>
       </c>
@@ -8124,7 +8116,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
         <v>89</v>
       </c>
@@ -8151,7 +8143,7 @@
       <c r="T2" s="38"/>
       <c r="U2" s="38"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="13" x14ac:dyDescent="0.3">
       <c r="M3" s="39" t="s">
         <v>7</v>
       </c>
@@ -8180,7 +8172,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
       <c r="M4" s="41" t="s">
         <v>38</v>
@@ -8210,7 +8202,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C5" s="8"/>
       <c r="M5" s="38" t="s">
         <v>51</v>
@@ -8335,7 +8327,7 @@
         <v>Steel Production by Direct Reduced Iron</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="13" x14ac:dyDescent="0.3">
       <c r="E12" s="5" t="s">
         <v>13</v>
       </c>
@@ -8353,7 +8345,7 @@
         <v>Steel Production</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="13" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
@@ -8382,7 +8374,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="21.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="10" t="s">
         <v>40</v>
       </c>
@@ -8414,7 +8406,7 @@
       <c r="T14" s="42"/>
       <c r="U14" s="42"/>
     </row>
-    <row r="15" spans="1:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="10" t="s">
         <v>64</v>
       </c>
@@ -8463,7 +8455,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="38" t="str">
         <f>O18</f>
@@ -8517,7 +8509,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:21" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="38"/>
       <c r="C17" t="str">
         <f>O6</f>
@@ -8687,31 +8679,31 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:U28"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="2.6640625" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="42.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.88671875" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" customWidth="1"/>
-    <col min="19" max="19" width="13.44140625" customWidth="1"/>
-    <col min="20" max="20" width="13.88671875" customWidth="1"/>
-    <col min="21" max="21" width="8.44140625" customWidth="1"/>
+    <col min="12" max="12" width="2.6328125" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="42.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.90625" customWidth="1"/>
+    <col min="18" max="18" width="11.6328125" customWidth="1"/>
+    <col min="19" max="19" width="13.453125" customWidth="1"/>
+    <col min="20" max="20" width="13.90625" customWidth="1"/>
+    <col min="21" max="21" width="8.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:21" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B1" s="7" t="s">
         <v>52</v>
       </c>
@@ -8731,7 +8723,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" ht="31" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
         <v>89</v>
       </c>
@@ -8764,7 +8756,7 @@
       <c r="T2" s="38"/>
       <c r="U2" s="38"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" ht="13" x14ac:dyDescent="0.3">
       <c r="M3" s="39" t="s">
         <v>7</v>
       </c>
@@ -8793,7 +8785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:21" ht="22" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="23"/>
       <c r="C4" s="23"/>
       <c r="D4" s="23"/>
@@ -8827,7 +8819,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B5" s="23"/>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
@@ -8854,7 +8846,7 @@
       <c r="T5" s="38"/>
       <c r="U5" s="38"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" ht="13" x14ac:dyDescent="0.3">
       <c r="D8" s="5" t="s">
         <v>13</v>
       </c>
@@ -8877,7 +8869,7 @@
       <c r="T8" s="42"/>
       <c r="U8" s="42"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" ht="13" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
         <v>1</v>
       </c>
@@ -8937,7 +8929,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:21" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="11" t="s">
         <v>40</v>
       </c>
@@ -8995,7 +8987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:21" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="10" t="s">
         <v>64</v>
       </c>
@@ -9033,9 +9025,8 @@
       <c r="U11" s="41"/>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B12" s="45" t="str">
-        <f>Fuel_Code!A28&amp;LEFT(Fuel_Code!A33,1)</f>
-        <v>IIST</v>
+      <c r="B12" s="45" t="s">
+        <v>144</v>
       </c>
       <c r="C12" t="str">
         <f>SEC_Process!D16</f>
@@ -9144,19 +9135,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:I22"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="12.44140625" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="12.453125" customWidth="1"/>
+    <col min="10" max="10" width="7.36328125" customWidth="1"/>
+    <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B1" s="7" t="s">
         <v>52</v>
       </c>
@@ -9173,7 +9164,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
         <v>62</v>
       </c>
@@ -9189,14 +9180,14 @@
         <v>RS 2015</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" ht="13" x14ac:dyDescent="0.3">
       <c r="C5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="13" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>59</v>
       </c>
@@ -9245,7 +9236,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="10" t="s">
         <v>64</v>
       </c>
